--- a/Data/Testcases/Testdata.xlsx
+++ b/Data/Testcases/Testdata.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\FrozenChlorine\Data\Testcases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F5EE36-295D-468C-9830-BB19ABFA0508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7207B0B-A2C6-4434-9B6C-408BB6E7DCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="1665" windowWidth="19875" windowHeight="12705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2265" yWindow="3585" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardOperations" sheetId="1" r:id="rId1"/>
+    <sheet name="Unit_ParseTermToList" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
   <si>
     <t>ID</t>
   </si>
@@ -77,6 +78,18 @@
   </si>
   <si>
     <t>DecimalSeparator</t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>exp_CharacterList</t>
+  </si>
+  <si>
+    <t>exp_Negate</t>
   </si>
 </sst>
 </file>
@@ -553,4 +566,105 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8C1169-06BD-4BD6-9602-AB5684D80F22}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>-1.23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>1.23</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>